--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. TRES CANTOS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. TRES CANTOS.xlsx
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5901</v>
+        <v>15.6461</v>
       </c>
       <c r="E2" t="n">
-        <v>15.0905</v>
+        <v>10.5876</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4997</v>
+        <v>5.0587</v>
       </c>
       <c r="G2" t="n">
-        <v>9.9847</v>
+        <v>12.34</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7161</v>
+        <v>-0.1552999999999998</v>
       </c>
       <c r="I2" t="n">
-        <v>5.268599999999999</v>
+        <v>12.4953</v>
       </c>
       <c r="J2" t="n">
-        <v>12.6741</v>
+        <v>16.2561</v>
       </c>
       <c r="K2" t="n">
-        <v>5.189299999999999</v>
+        <v>2.361399999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>7.484599999999999</v>
+        <v>13.8947</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6893</v>
+        <v>-3.9161</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4732</v>
+        <v>-2.5166</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.216</v>
+        <v>-1.3994</v>
       </c>
       <c r="P2" t="n">
-        <v>4.2012</v>
+        <v>-3.3105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2003</v>
+        <v>-15.7737</v>
       </c>
       <c r="R2" t="n">
-        <v>5.4015</v>
+        <v>12.4631</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5952000000000001</v>
+        <v>-1.879</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8423</v>
+        <v>-1.6714</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2471</v>
+        <v>-0.2077999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9994</v>
+        <v>8.495900000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>4.459</v>
+        <v>11.7763</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.4596</v>
+        <v>-3.2806</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7775</v>
+        <v>11.4881</v>
       </c>
       <c r="E3" t="n">
-        <v>1.717</v>
+        <v>9.428100000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0606</v>
+        <v>2.0601</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3588</v>
+        <v>9.5747</v>
       </c>
       <c r="H3" t="n">
-        <v>2.082</v>
+        <v>4.47</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.4408</v>
+        <v>5.104699999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4071000000000002</v>
+        <v>15.0435</v>
       </c>
       <c r="K3" t="n">
-        <v>2.183</v>
+        <v>6.4327</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.5901</v>
+        <v>8.610799999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04830000000000001</v>
+        <v>-5.469</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.101</v>
+        <v>-1.9628</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1493</v>
+        <v>-3.5063</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0002</v>
+        <v>0.9735999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2004</v>
+        <v>-10.7105</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2006</v>
+        <v>11.6843</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3364</v>
+        <v>-0.9948999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9248000000000001</v>
+        <v>-2.1281</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5884</v>
+        <v>1.1333</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7997</v>
+        <v>1.9347</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3996</v>
+        <v>7.2232</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5999</v>
+        <v>-5.2884</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.458</v>
+        <v>8.202300000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3754</v>
+        <v>6.555499999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.9175</v>
+        <v>1.6469</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5729</v>
+        <v>1.8101</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4959</v>
+        <v>1.4591</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07699999999999996</v>
+        <v>0.3509000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>6.2318</v>
+        <v>2.4488</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6608</v>
+        <v>1.3219</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5711</v>
+        <v>1.127</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.659</v>
+        <v>-0.6389</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1648</v>
+        <v>0.1372000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4941</v>
+        <v>-0.776</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2001</v>
+        <v>0.3894000000000002</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0009</v>
+        <v>-6.2316</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2009</v>
+        <v>6.621</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4643</v>
+        <v>9.562799999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.05539999999999998</v>
+        <v>9.499699999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5196999999999999</v>
+        <v>0.06310000000000004</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7793999999999999</v>
+        <v>-3.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1998</v>
+        <v>0.8385</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.9792</v>
+        <v>-4.3985</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1998</v>
+        <v>4.0656</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1998</v>
+        <v>3.3147</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.7508000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1998</v>
+        <v>0.4920999999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.3742</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1998</v>
+        <v>-0.8821</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1998</v>
+        <v>1.7946</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.4215</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1998</v>
+        <v>0.3731</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.3024</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.04729999999999998</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.2552</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.5579</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.5315</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.158700000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.078</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.08079999999999998</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>D. GONZALEZ  LONGARELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1353</v>
+        <v>3.0553</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4016</v>
+        <v>3.0553</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5368</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1716</v>
+        <v>3.0553</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4802</v>
+        <v>1.2316</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.6915</v>
+        <v>1.8237</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.425</v>
+        <v>3.0553</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7216</v>
+        <v>1.2316</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1465</v>
+        <v>1.8237</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7467</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2017</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5449</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6007</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2006</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.8014</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5267</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1848</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3418</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1795</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0392</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5999</v>
+        <v>2.4329</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5999</v>
+        <v>-8.068200000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>10.5011</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5999</v>
+        <v>-6.8116</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5999</v>
+        <v>-5.5664</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5999</v>
+        <v>-3.2639</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.3649</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5999</v>
+        <v>-3.6287</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-3.5475</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.6099</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.9377</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7263</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-10.3211</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>13.0474</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>8.349600000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.1779</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.172000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.8315</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.339</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-4.170500000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3618999999999999</v>
+        <v>2.377999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6919000000000001</v>
+        <v>-0.6594999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.33</v>
+        <v>3.0375</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7828</v>
+        <v>-0.8306999999999998</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.02690000000000003</v>
+        <v>1.3379</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7559</v>
+        <v>-2.1688</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7323</v>
+        <v>0.8096000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3017</v>
+        <v>1.1653</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.034</v>
+        <v>-0.3557000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05060000000000001</v>
+        <v>-1.6403</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3286</v>
+        <v>0.1726</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2781</v>
+        <v>-1.813</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4002</v>
+        <v>0.5843</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-4.8684</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4002</v>
+        <v>5.4526</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0208</v>
+        <v>1.0725</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0404</v>
+        <v>0.9571000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0196</v>
+        <v>0.1153999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.5521</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4422</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8900000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CANAS</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6073</v>
+        <v>1.2158</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2531</v>
+        <v>1.2158</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3543</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4419999999999999</v>
+        <v>1.2158</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6329</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0749</v>
+        <v>1.2158</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1234</v>
+        <v>1.2158</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8834000000000001</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.24</v>
+        <v>1.2158</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5654</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2504</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3148</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2003</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0009</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8005</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7752</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1049</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3297</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7907000000000001</v>
+        <v>-2.6315</v>
       </c>
       <c r="E10" t="n">
-        <v>2.739</v>
+        <v>-4.7089</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5297</v>
+        <v>2.0777</v>
       </c>
       <c r="G10" t="n">
-        <v>0.178</v>
+        <v>-6.497199999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0338</v>
+        <v>-2.0127</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2118</v>
+        <v>-4.4848</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6651</v>
+        <v>-4.3989</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5453</v>
+        <v>-0.3719</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1199</v>
+        <v>-4.027</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4871</v>
+        <v>-2.0984</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-1.6406</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9079999999999999</v>
+        <v>-0.4578</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.9474</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-1.5578</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0003</v>
+        <v>3.5051</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9505</v>
+        <v>1.536</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0741</v>
+        <v>1.248</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1236</v>
+        <v>0.2882</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.9192</v>
+        <v>0.3826</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.9192</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="11">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6422</v>
+        <v>-2.8108</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8478</v>
+        <v>-4.8469</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2057</v>
+        <v>2.0361</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8403</v>
+        <v>-4.4483</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9671</v>
+        <v>-1.0524</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1268</v>
+        <v>-3.3958</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3322</v>
+        <v>-3.5328</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.974</v>
+        <v>-1.1263</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6418</v>
+        <v>-2.4065</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5081</v>
+        <v>-0.9156</v>
       </c>
       <c r="N11" t="n">
-        <v>0.006900000000000017</v>
+        <v>0.07369999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.515</v>
+        <v>-0.9894000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6002000000000001</v>
+        <v>1.1683</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6002000000000001</v>
+        <v>3.3105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1423</v>
+        <v>0.08630000000000004</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.3932</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3734</v>
+        <v>0.4798</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2598</v>
+        <v>0.3825999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2598</v>
+        <v>-0.8385</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>D. FERNANDEZ CANAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8422</v>
+        <v>-4.748400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6428</v>
+        <v>-8.519500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1995</v>
+        <v>3.771</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6999</v>
+        <v>-2.3715</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5224</v>
+        <v>-1.5085</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1775</v>
+        <v>-0.8629</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.578</v>
+        <v>-2.1681</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.658</v>
+        <v>-1.5366</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08</v>
+        <v>-0.6317</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1219</v>
+        <v>-0.2034000000000002</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1356</v>
+        <v>0.02789999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2575</v>
+        <v>-0.2314000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.0003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-6.2316</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.142</v>
+        <v>0.6771</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0645</v>
+        <v>-0.01649999999999996</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0776</v>
+        <v>0.6934999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-4.2222</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.1031</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-4.1191</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. GONZALEZ LONGARELA</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.573</v>
+        <v>-5.5321</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6842</v>
+        <v>-5.5897</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1111000000000001</v>
+        <v>0.0576000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.1333</v>
+        <v>2.2695</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.27</v>
+        <v>0.4365999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1367000000000003</v>
+        <v>1.8327</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8233000000000001</v>
+        <v>6.2318</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.383</v>
+        <v>2.6534</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5598</v>
+        <v>3.5786</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.31</v>
+        <v>-3.9625</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8869999999999999</v>
+        <v>-2.2167</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.423</v>
+        <v>-1.7455</v>
       </c>
       <c r="P13" t="n">
-        <v>1.2004</v>
+        <v>0.5842000000000003</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2006</v>
+        <v>-8.763200000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>3.401</v>
+        <v>9.3474</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8007</v>
+        <v>-5.3847</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9201</v>
+        <v>-4.2796</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8807</v>
+        <v>-1.1052</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1606</v>
+        <v>-3.001</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2598</v>
+        <v>1.2211</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.09919999999999995</v>
+        <v>-4.2221</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.143000000000001</v>
+        <v>-11.0625</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5987999999999998</v>
+        <v>-9.9259</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.5441</v>
+        <v>-1.1366</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9377</v>
+        <v>-8.2804</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4955</v>
+        <v>-5.4538</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4421999999999997</v>
+        <v>-2.8266</v>
       </c>
       <c r="J14" t="n">
-        <v>1.586</v>
+        <v>-4.2204</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3271000000000001</v>
+        <v>-4.853999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2589</v>
+        <v>0.6335</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.5237</v>
+        <v>-4.0599</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8226</v>
+        <v>-0.5996999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7011</v>
+        <v>-3.4602</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8005</v>
+        <v>-0.3894999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2004</v>
+        <v>-8.5684</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0009</v>
+        <v>8.178900000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0063</v>
+        <v>2.8744</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9844999999999999</v>
+        <v>3.6798</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0218</v>
+        <v>-0.8054999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.9994</v>
+        <v>-5.2668</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.8168</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.9994</v>
+        <v>-4.4501</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>D. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.169</v>
+        <v>-13.7968</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.9214</v>
+        <v>-13.1537</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7524</v>
+        <v>-0.643</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.3403</v>
+        <v>-10.0124</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.2001</v>
+        <v>-9.033799999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.1401</v>
+        <v>-0.9787000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.0027</v>
+        <v>-4.0564</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.5705</v>
+        <v>-5.621</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4322</v>
+        <v>1.5644</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3375</v>
+        <v>-5.956</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6296</v>
+        <v>-3.4129</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.708</v>
+        <v>-2.543</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2000999999999999</v>
+        <v>9.999999999993348e-05</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.0012</v>
+        <v>-7.9842</v>
       </c>
       <c r="R15" t="n">
-        <v>4.2012</v>
+        <v>7.9842</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2910000000000001</v>
+        <v>-1.7033</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8227</v>
+        <v>-1.3925</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5317</v>
+        <v>-0.3107</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6801999999999999</v>
+        <v>-2.0812</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4204000000000001</v>
+        <v>-2.3607</v>
       </c>
     </row>
     <row r="16">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>6.631299999999993</v>
+        <v>7.901999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>9.679999999999998</v>
+        <v>-21.3153</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0488</v>
+        <v>29.2179</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.1714</v>
+        <v>-8.494599999999998</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.06909999999999927</v>
+        <v>-10.1523</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.102300000000001</v>
+        <v>1.657000000000005</v>
       </c>
       <c r="J16" t="n">
-        <v>16.7795</v>
+        <v>25.215</v>
       </c>
       <c r="K16" t="n">
-        <v>7.226699999999998</v>
+        <v>3.442899999999998</v>
       </c>
       <c r="L16" t="n">
-        <v>9.552999999999999</v>
+        <v>21.77199999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-20.951</v>
+        <v>-33.71</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.295500000000001</v>
+        <v>-13.5951</v>
       </c>
       <c r="O16" t="n">
-        <v>-13.655</v>
+        <v>-20.1149</v>
       </c>
       <c r="P16" t="n">
-        <v>10.003</v>
+        <v>6.815700000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-20.0059</v>
+        <v>-84.71050000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>30.0087</v>
+        <v>91.526</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6784</v>
+        <v>17.35550000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7693</v>
+        <v>11.7592</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0911</v>
+        <v>5.596900000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8785999999999996</v>
+        <v>-7.773799999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>10.1368</v>
+        <v>26.421</v>
       </c>
       <c r="X16" t="n">
-        <v>-11.0154</v>
+        <v>-34.1949</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. TRES CANTOS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. TRES CANTOS.xlsx
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>15.6461</v>
+        <v>19.6559</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5876</v>
+        <v>13.7874</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0587</v>
+        <v>5.8686</v>
       </c>
       <c r="G2" t="n">
         <v>12.34</v>
@@ -610,13 +610,13 @@
         <v>12.4631</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.879</v>
+        <v>2.1306</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.6714</v>
+        <v>1.5285</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2077999999999999</v>
+        <v>0.602</v>
       </c>
       <c r="V2" t="n">
         <v>8.495900000000001</v>
@@ -643,13 +643,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>11.4881</v>
+        <v>14.6608</v>
       </c>
       <c r="E3" t="n">
-        <v>9.428100000000001</v>
+        <v>12.4525</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0601</v>
+        <v>2.2084</v>
       </c>
       <c r="G3" t="n">
         <v>9.5747</v>
@@ -688,13 +688,13 @@
         <v>11.6843</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9948999999999999</v>
+        <v>2.1777</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.1281</v>
+        <v>0.8962000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1333</v>
+        <v>1.2817</v>
       </c>
       <c r="V3" t="n">
         <v>1.9347</v>
@@ -721,13 +721,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>8.202300000000001</v>
+        <v>3.6113</v>
       </c>
       <c r="E4" t="n">
-        <v>6.555499999999999</v>
+        <v>0.8980000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6469</v>
+        <v>2.7132</v>
       </c>
       <c r="G4" t="n">
         <v>1.8101</v>
@@ -766,13 +766,13 @@
         <v>6.621</v>
       </c>
       <c r="S4" t="n">
-        <v>9.562799999999999</v>
+        <v>4.971699999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>9.499699999999999</v>
+        <v>3.8423</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06310000000000004</v>
+        <v>1.1296</v>
       </c>
       <c r="V4" t="n">
         <v>-3.56</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>D. GONZALEZ  LONGARELA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0656</v>
+        <v>3.0553</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3147</v>
+        <v>3.0553</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7508000000000001</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4920999999999998</v>
+        <v>3.0553</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3742</v>
+        <v>1.2316</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8821</v>
+        <v>1.8237</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7946</v>
+        <v>3.0553</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4215</v>
+        <v>1.2316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3731</v>
+        <v>1.8237</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3024</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.04729999999999998</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2552</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.5579</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5315</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.158700000000001</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.078</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08079999999999998</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0553</v>
+        <v>2.8712</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0553</v>
+        <v>1.9811</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.8899999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0553</v>
+        <v>0.4920999999999998</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2316</v>
+        <v>1.3742</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8237</v>
+        <v>-0.8821</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0553</v>
+        <v>1.7946</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2316</v>
+        <v>1.4215</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8237</v>
+        <v>0.3731</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.3024</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.04729999999999998</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.2552</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.5579</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.5315</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.9643</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.7442</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2198</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4329</v>
+        <v>2.729100000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-8.068200000000001</v>
+        <v>-0.7352999999999996</v>
       </c>
       <c r="F7" t="n">
-        <v>10.5011</v>
+        <v>3.4643</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.8116</v>
+        <v>-0.8306999999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2452</v>
+        <v>1.3379</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.5664</v>
+        <v>-2.1688</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.2639</v>
+        <v>0.8096000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3649</v>
+        <v>1.1653</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.6287</v>
+        <v>-0.3557000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.5475</v>
+        <v>-1.6403</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6099</v>
+        <v>0.1726</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9377</v>
+        <v>-1.813</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7263</v>
+        <v>0.5843</v>
       </c>
       <c r="Q7" t="n">
-        <v>-10.3211</v>
+        <v>-4.8684</v>
       </c>
       <c r="R7" t="n">
-        <v>13.0474</v>
+        <v>5.4526</v>
       </c>
       <c r="S7" t="n">
-        <v>8.349600000000001</v>
+        <v>1.4235</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1779</v>
+        <v>0.8815000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>5.172000000000001</v>
+        <v>0.5419</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8315</v>
+        <v>1.5521</v>
       </c>
       <c r="W7" t="n">
-        <v>2.339</v>
+        <v>2.4422</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.170500000000001</v>
+        <v>-0.8900000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2.377999999999999</v>
+        <v>1.2158</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6594999999999999</v>
+        <v>1.2158</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0375</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8306999999999998</v>
+        <v>1.2158</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3379</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1688</v>
+        <v>1.2158</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8096000000000001</v>
+        <v>1.2158</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1653</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3557000000000001</v>
+        <v>1.2158</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6403</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1726</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.813</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5843</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.8684</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5.4526</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0725</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9571000000000001</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1153999999999999</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5521</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4422</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8900000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2158</v>
+        <v>-0.7528000000000006</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2158</v>
+        <v>-9.0307</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>8.2781</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2158</v>
+        <v>-6.8116</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2158</v>
+        <v>-5.5664</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2158</v>
+        <v>-3.2639</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.3649</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2158</v>
+        <v>-3.6287</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-3.5475</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.6099</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-1.9377</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.7263</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-10.3211</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>13.0474</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5.1639</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.2152</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.9489</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.8315</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.339</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-4.170500000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6315</v>
+        <v>-0.8517000000000006</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7089</v>
+        <v>-2.1768</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0777</v>
+        <v>1.3251</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.497199999999999</v>
+        <v>2.2695</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0127</v>
+        <v>0.4365999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.4848</v>
+        <v>1.8327</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.3989</v>
+        <v>6.2318</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3719</v>
+        <v>2.6534</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.027</v>
+        <v>3.5786</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0984</v>
+        <v>-3.9625</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6406</v>
+        <v>-2.2167</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4578</v>
+        <v>-1.7455</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9474</v>
+        <v>0.5842000000000003</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.5578</v>
+        <v>-8.763200000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>3.5051</v>
+        <v>9.3474</v>
       </c>
       <c r="S10" t="n">
-        <v>1.536</v>
+        <v>-0.7042</v>
       </c>
       <c r="T10" t="n">
-        <v>1.248</v>
+        <v>-0.8666</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2882</v>
+        <v>0.1623999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3826</v>
+        <v>-3.001</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3826</v>
+        <v>-4.2221</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8108</v>
+        <v>-1.8232</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8469</v>
+        <v>-4.1869</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0361</v>
+        <v>2.3638</v>
       </c>
       <c r="G11" t="n">
         <v>-4.4483</v>
@@ -1312,13 +1312,13 @@
         <v>3.3105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08630000000000004</v>
+        <v>1.0741</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3932</v>
+        <v>0.2668</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4798</v>
+        <v>0.8073</v>
       </c>
       <c r="V11" t="n">
         <v>0.3825999999999999</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CANAS</t>
+          <t>F. GOMEZ DE ENTERRIA LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.748400000000001</v>
+        <v>-3.2162</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.519500000000001</v>
+        <v>-5.4824</v>
       </c>
       <c r="F12" t="n">
-        <v>3.771</v>
+        <v>2.266</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3715</v>
+        <v>-6.497199999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5085</v>
+        <v>-2.0127</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8629</v>
+        <v>-4.4848</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1681</v>
+        <v>-4.3989</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5366</v>
+        <v>-0.3719</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6317</v>
+        <v>-4.027</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2034000000000002</v>
+        <v>-2.0984</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02789999999999999</v>
+        <v>-1.6406</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2314000000000001</v>
+        <v>-0.4578</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1684</v>
+        <v>1.9474</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.2316</v>
+        <v>-1.5578</v>
       </c>
       <c r="R12" t="n">
-        <v>7.4</v>
+        <v>3.5051</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6771</v>
+        <v>0.9510000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.01649999999999996</v>
+        <v>0.4745</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6934999999999999</v>
+        <v>0.4766</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.2222</v>
+        <v>0.3826</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1031</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.1191</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>D. FERNANDEZ CANAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5321</v>
+        <v>-3.7227</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.5897</v>
+        <v>-7.911</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0576000000000001</v>
+        <v>4.1885</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2695</v>
+        <v>-2.3715</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4365999999999999</v>
+        <v>-1.5085</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8327</v>
+        <v>-0.8629</v>
       </c>
       <c r="J13" t="n">
-        <v>6.2318</v>
+        <v>-2.1681</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6534</v>
+        <v>-1.5366</v>
       </c>
       <c r="L13" t="n">
-        <v>3.5786</v>
+        <v>-0.6317</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.9625</v>
+        <v>-0.2034000000000002</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.2167</v>
+        <v>0.02789999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7455</v>
+        <v>-0.2314000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5842000000000003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.763200000000001</v>
+        <v>-6.2316</v>
       </c>
       <c r="R13" t="n">
-        <v>9.3474</v>
+        <v>7.4</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.3847</v>
+        <v>1.7025</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.2796</v>
+        <v>0.5915999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1052</v>
+        <v>1.1109</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.001</v>
+        <v>-4.2222</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2211</v>
+        <v>-0.1031</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.2221</v>
+        <v>-4.1191</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>D. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.0625</v>
+        <v>-11.1131</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.9259</v>
+        <v>-10.8751</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1366</v>
+        <v>-0.2381000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.2804</v>
+        <v>-10.0124</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.4538</v>
+        <v>-9.033799999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.8266</v>
+        <v>-0.9787000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.2204</v>
+        <v>-4.0564</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.853999999999999</v>
+        <v>-5.621</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6335</v>
+        <v>1.5644</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.0599</v>
+        <v>-5.956</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5996999999999999</v>
+        <v>-3.4129</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.4602</v>
+        <v>-2.543</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3894999999999999</v>
+        <v>9.999999999993348e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.5684</v>
+        <v>-7.9842</v>
       </c>
       <c r="R14" t="n">
-        <v>8.178900000000001</v>
+        <v>7.9842</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8744</v>
+        <v>0.9803999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6798</v>
+        <v>0.8862000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8054999999999999</v>
+        <v>0.09429999999999994</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.2668</v>
+        <v>-2.0812</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.8168</v>
+        <v>0.2795</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.4501</v>
+        <v>-2.3607</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. GONZALEZ LONGARELA</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.7968</v>
+        <v>-12.6209</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.1537</v>
+        <v>-11.8336</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.643</v>
+        <v>-0.7873000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.0124</v>
+        <v>-8.2804</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.033799999999999</v>
+        <v>-5.4538</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9787000000000001</v>
+        <v>-2.8266</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.0564</v>
+        <v>-4.2204</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.621</v>
+        <v>-4.853999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5644</v>
+        <v>0.6335</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.956</v>
+        <v>-4.0599</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.4129</v>
+        <v>-0.5996999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.543</v>
+        <v>-3.4602</v>
       </c>
       <c r="P15" t="n">
-        <v>9.999999999993348e-05</v>
+        <v>-0.3894999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.9842</v>
+        <v>-8.5684</v>
       </c>
       <c r="R15" t="n">
-        <v>7.9842</v>
+        <v>8.178900000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7033</v>
+        <v>1.3158</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3925</v>
+        <v>1.7721</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3107</v>
+        <v>-0.4561999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.0812</v>
+        <v>-5.2668</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2795</v>
+        <v>-0.8168</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3607</v>
+        <v>-4.4501</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>7.901999999999999</v>
+        <v>13.69879999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-21.3153</v>
+        <v>-18.8417</v>
       </c>
       <c r="F16" t="n">
-        <v>29.2179</v>
+        <v>32.5406</v>
       </c>
       <c r="G16" t="n">
         <v>-8.494599999999998</v>
@@ -1672,19 +1672,19 @@
         <v>-10.1523</v>
       </c>
       <c r="I16" t="n">
-        <v>1.657000000000005</v>
+        <v>1.657000000000003</v>
       </c>
       <c r="J16" t="n">
         <v>25.215</v>
       </c>
       <c r="K16" t="n">
-        <v>3.442899999999998</v>
+        <v>3.4429</v>
       </c>
       <c r="L16" t="n">
-        <v>21.77199999999999</v>
+        <v>21.772</v>
       </c>
       <c r="M16" t="n">
-        <v>-33.71</v>
+        <v>-33.71000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>-13.5951</v>
@@ -1696,22 +1696,22 @@
         <v>6.815700000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-84.71050000000001</v>
+        <v>-84.7105</v>
       </c>
       <c r="R16" t="n">
-        <v>91.526</v>
+        <v>91.52600000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>17.35550000000001</v>
+        <v>23.1513</v>
       </c>
       <c r="T16" t="n">
-        <v>11.7592</v>
+        <v>14.2325</v>
       </c>
       <c r="U16" t="n">
-        <v>5.596900000000001</v>
+        <v>8.9192</v>
       </c>
       <c r="V16" t="n">
-        <v>-7.773799999999999</v>
+        <v>-7.7738</v>
       </c>
       <c r="W16" t="n">
         <v>26.421</v>
